--- a/dw/silver/pilot_test.xlsx
+++ b/dw/silver/pilot_test.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="57">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -179,6 +179,21 @@
   </si>
   <si>
     <t xml:space="preserve">Transação referente ao crédito nº 8136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transação referente ao crédito nº 0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">teste </t>
   </si>
 </sst>
 </file>
@@ -1314,8 +1329,40 @@
         <v>8136</v>
       </c>
     </row>
-    <row r="1047327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1047328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>999</v>
+      </c>
+    </row>
     <row r="1047329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1047330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1047331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
